--- a/data/seed/portfolio/L-2025-2207/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-2207/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -558,40 +558,40 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>8292000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>17104000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №48/26 от 02.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №201/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,33 +599,33 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>22943000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>8852000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shahrisabz Avto Ehtiyot XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>306929805</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000432474335001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9222 03.07.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №48/26, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -640,23 +640,23 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>14589000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>13099000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -666,14 +666,14 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5376</t>
+          <t>Оплата за упаковочные материалы, с/ф №6939</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -681,33 +681,33 @@
           <t>103</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>21815000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>67598000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №92/26</t>
+          <t>Оплата за продукцию по дог. №78/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -724,31 +724,31 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>12829000</v>
+        <v>60205000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Shartnoma №50/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №33/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -765,31 +765,31 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>11576000</v>
+        <v>12331000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7584 06.07.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №66/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -805,32 +805,32 @@
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>24367000</v>
+        <v>5171000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Xiva Logistik MChJ</t>
+          <t>Buxoro Tekstil MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>234896196</t>
+          <t>234401967</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000371743824001</t>
+          <t>20208000064073879001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9913</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №270/26</t>
         </is>
       </c>
     </row>
@@ -846,32 +846,32 @@
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>32512000</v>
+        <v>43100000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №96/26</t>
+          <t>Оплата за транспортные услуги по договору №96/26</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №1369</t>
         </is>
       </c>
     </row>
@@ -922,23 +922,23 @@
           <t>109</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>18269000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>2571000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №284/26 от 07.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -964,32 +964,32 @@
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>4738000</v>
+        <v>3769000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>266148204</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000217756169001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №50/21</t>
+          <t>Оплата за транспортные услуги по договору №142/26</t>
         </is>
       </c>
     </row>
@@ -1005,39 +1005,39 @@
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>9229000</v>
+        <v>320742000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №142/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8715</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,23 +1045,23 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>16936000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>126274000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №284/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №8/26 от 08.07.2026</t>
         </is>
       </c>
     </row>
@@ -1086,33 +1086,33 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>19975000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>4738000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Bekobod Qurilish XK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>274288289</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000521839114001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shartnoma №8/26 bo'yicha oldindan to'lov</t>
+          <t>Аренда помещения за июль, дог. №65/23</t>
         </is>
       </c>
     </row>
@@ -1128,32 +1128,32 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>16512000</v>
+        <v>3926000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №295/26</t>
+          <t>Оплата за транспортные услуги по договору №295/26</t>
         </is>
       </c>
     </row>
@@ -1170,31 +1170,31 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>10100000</v>
+        <v>73857000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №2/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №2/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1209,23 +1209,23 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>9754000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>24597000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №97/26</t>
+          <t>Предоплата за товар по дог. №71/26 от 13.07.2026</t>
         </is>
       </c>
     </row>
@@ -1251,39 +1251,39 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20743000</v>
+        <v>3384000</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №43/26, QQS bilan</t>
+          <t>Оплата за товары согласно счет-фактуре №1605</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1292,32 +1292,32 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>7185000</v>
+        <v>6662000</v>
       </c>
       <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №1850</t>
         </is>
       </c>
     </row>
@@ -1332,33 +1332,33 @@
           <t>119</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>7185000</v>
-      </c>
-      <c r="D29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n">
+        <v>10936000</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Оплата по счет-фактуре №356 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1374,22 +1374,22 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>22121000</v>
+        <v>2373000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nurafshon Dori-Darmon MChJ</t>
+          <t>Oydin Plastik MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>353894823</t>
+          <t>289619633</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000867104413001</t>
+          <t>20208000174382470001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1399,14 +1399,14 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №41/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №4713</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1414,40 +1414,40 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>9493000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>7185000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №38/26, QQS 12%</t>
+          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА ИЮНЬ 2026 Г.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1456,39 +1456,39 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>8317000</v>
+        <v>7185000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №134</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1498,38 +1498,38 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>63878000</v>
+        <v>13670000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2104 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №102/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1539,38 +1539,38 @@
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>24494000</v>
+        <v>10748000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №118/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №3031 от 16.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1578,23 +1578,23 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>16050000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>12313000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №139/26 от 20.07.2026</t>
+          <t>Предоплата за материалы по договору №96/26</t>
         </is>
       </c>
     </row>
@@ -1619,33 +1619,33 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>27407000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>26765000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chust Ip-Kalava MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>314114267</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000291678153001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №4/26</t>
+          <t>Shartnoma №139/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1660,33 +1660,33 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>93596000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>10995000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Angren Mato MChJ</t>
+          <t>Xiva Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>244573432</t>
+          <t>326926229</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000147986957001</t>
+          <t>20208000034722157001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №205/26, QQS BILAN</t>
+          <t>Предоплата за товар по договору №269/26 от 20.07.2026</t>
         </is>
       </c>
     </row>
@@ -1702,17 +1702,22 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>98100000</v>
+        <v>4682000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2207)</t>
+          <t>Namangan Avto Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>289482378</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16307000204551232417</t>
+          <t>20208000710441309001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1722,14 +1727,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2207 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №4/26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1737,40 +1742,35 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>52758000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>98100000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>326149159</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2207)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>16307000204551232417</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5220 21.07.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-2207 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,33 +1778,33 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>7641000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>23048000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Mato XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>267547195</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000704022068001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>Оплата за товар по счет-фактуре №7388 от 22.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1820,32 +1820,32 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>16702000</v>
+        <v>4334000</v>
       </c>
       <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №139/26, QQS BILAN</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №139/26 ОТ 22.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -1861,39 +1861,39 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>22569000</v>
+        <v>7558000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №243/26</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1902,32 +1902,32 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>36033000</v>
+        <v>10923000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №48/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №3011</t>
         </is>
       </c>
     </row>
@@ -1944,38 +1944,38 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>34630000</v>
+        <v>11847000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Nukus Mato XK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>267547195</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000704022068001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №255/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,31 +1985,31 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>24403000</v>
+        <v>29880000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6866</t>
+          <t>Shartnoma №172/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -2026,31 +2026,31 @@
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>161347000</v>
+        <v>29664000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2337</t>
+          <t>Оплата за товар по с/ф №588 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2065,33 +2065,33 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>2961000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>20578000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000815144355001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Оплата по счет-фактуре №4320 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -2107,22 +2107,22 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>28450000</v>
+        <v>2961000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gulshan Yog' Zavodi MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>392801798</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000155724205001</t>
+          <t>20208000802611443001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2132,14 +2132,14 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9917</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>92953000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>10008000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Mehnat Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>255105855</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000429346218001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3260 29.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по дог. №295/26 от 27.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,33 +2188,33 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>14703000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>21285000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Oltin Vodiy Savdo MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>257343281</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000798695782001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Shartnoma №102/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №9917</t>
         </is>
       </c>
     </row>
@@ -2229,33 +2229,33 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>10780000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>18329000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Xiva Logistik MChJ</t>
+          <t>Bunyodkor Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>234896196</t>
+          <t>244008893</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000371743824001</t>
+          <t>20208000320157345001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №221/26</t>
+          <t>Оплата за товар по с/ф №8963 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2271,32 +2271,32 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>27408000</v>
+        <v>5026000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Xiva Logistik MChJ</t>
+          <t>Buxoro Tekstil MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>234896196</t>
+          <t>234401967</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000371743824001</t>
+          <t>20208000064073879001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №12/26</t>
+          <t>Предоплата за материалы по договору №221/26</t>
         </is>
       </c>
     </row>
@@ -2312,32 +2312,32 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>40696000</v>
+        <v>6243000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bog'ishamol Meva Eksport MChJ</t>
+          <t>Buxoro Tekstil MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>256016118</t>
+          <t>234401967</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000519184114001</t>
+          <t>20208000064073879001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №167/26 от 29.07.2026, НДС 12%</t>
+          <t>Предоплата за материалы по договору №12/26</t>
         </is>
       </c>
     </row>
@@ -2352,33 +2352,33 @@
           <t>144</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>9177000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>2530000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Buxoro Tekstil MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>234401967</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000064073879001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №568 30.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №66/26</t>
         </is>
       </c>
     </row>
@@ -2395,31 +2395,31 @@
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>12371000</v>
+        <v>41419000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №9825 31.07.2026, QQS BILAN</t>
+          <t>Оплата за продукцию по договору №267/26, НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2434,40 +2434,35 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>10182000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>326149159</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №83/26, QQS 12%</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2475,28 +2470,33 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>88261000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qarshi Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Оплата за товар по счет-фактуре №9092 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
@@ -2513,38 +2513,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>43881000</v>
+        <v>31752000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Shartnoma №192/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №5397 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2553,39 +2553,34 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>11203000</v>
+        <v>51451000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nurafshon Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>353894823</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000867104413001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №189/26</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №8632</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2593,40 +2588,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>53573000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>30344000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №299/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №278/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2636,38 +2631,38 @@
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>2458000</v>
+        <v>14241000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Ishonch Logistik MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>282316791</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000143593177001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №103/26 от 04.08.2026</t>
+          <t>Оплата за товар по с/ф №619 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2675,40 +2670,40 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>10532000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>11895000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nurafshon Dori-Darmon MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>353894823</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000867104413001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №438</t>
+          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2717,34 +2712,39 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>51451000</v>
+        <v>4627000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bekobod Qurilish XK</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>274288289</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000521839114001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №4302</t>
+          <t>Арендная плата за август 2026 г. по договору №65/23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2753,39 +2753,39 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>45581000</v>
+        <v>9696000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №216/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №140/26</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2795,38 +2795,38 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>3046000</v>
+        <v>47215000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №103/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №15/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>06.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2834,23 +2834,23 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>22066000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>25259000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2860,14 +2860,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №56/26</t>
+          <t>Оплата за товар по с/ф №3384 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2877,31 +2877,31 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>8213000</v>
+        <v>25121000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №241/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №170/26 от 10.08.2026</t>
         </is>
       </c>
     </row>
@@ -2916,23 +2916,23 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>11105000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>10766000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2156 10.08.2026, QQS bilan</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №104/26</t>
         </is>
       </c>
     </row>
@@ -2958,39 +2958,39 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>4627000</v>
+        <v>13444000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>266148204</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000217756169001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Ijara haqi avgust oyi uchun, shartn. №50/21</t>
+          <t>Оплата за упаковочные материалы, с/ф №6711</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2999,39 +2999,39 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>11236000</v>
+        <v>19070000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Xiva Logistik MChJ</t>
+          <t>Namangan Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>234896196</t>
+          <t>289482378</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000371743824001</t>
+          <t>20208000710441309001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №104/26</t>
+          <t>Оплата за товары согласно с/ф №1696</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3039,33 +3039,33 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>5406000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>61371000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Mehnat Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>255105855</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000429346218001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4249 за поставленный товар</t>
+          <t>Оплата за транспортные услуги по договору №156/26</t>
         </is>
       </c>
     </row>
@@ -3081,39 +3081,39 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>8730000</v>
+        <v>8178000</v>
       </c>
       <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gulshan Yog' Zavodi MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>392801798</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000155724205001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №28/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №8941</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3123,38 +3123,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>2642000</v>
+        <v>10289000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Jizzax Meva Eksport XK</t>
+          <t>Ishonch Logistik MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>272675471</t>
+          <t>282316791</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000547040220001</t>
+          <t>20208000143593177001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Shartnoma №152/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №91/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3162,23 +3162,23 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>20929000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>11727000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3188,14 +3188,14 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Shartnoma №8/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartn. №21/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3203,23 +3203,23 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>16723000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>22685000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Shartnoma №232/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №279/26</t>
         </is>
       </c>
     </row>
@@ -3244,33 +3244,33 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>7016000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>17126000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Оплата по счет-фактуре №6414 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
     </row>
@@ -3327,39 +3327,39 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>9819000</v>
+        <v>7016000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Xiva Logistik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>234896196</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000371743824001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №280/26</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3367,23 +3367,23 @@
           <t>169</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>84424000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>55394000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Oqtosh Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>233823167</t>
+          <t>211426722</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000141435931001</t>
+          <t>20208000167815308001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3393,14 +3393,14 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №32/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №13/26</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3408,40 +3408,35 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>43383000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>98100000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>281194585</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2207)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>16307000204551232417</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shartnoma №41/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2025-2207 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3451,38 +3446,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>8236000</v>
+        <v>10773000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Nukus Mato XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>267547195</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000704022068001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №252/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №192/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3492,38 +3487,38 @@
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>6815000</v>
+        <v>10467000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Toshkent Metall Servis AJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>238365187</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000969766274001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Shartnoma №261/26 bo'yicha oldindn to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №280/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3532,39 +3527,39 @@
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>15829000</v>
+        <v>2892000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000802611443001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №12/26, QQS bilan</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3573,39 +3568,39 @@
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>19526000</v>
+        <v>7502000</v>
       </c>
       <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nurafshon Dori-Darmon MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>353894823</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000867104413001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №144/26</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3614,39 +3609,39 @@
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>109475000</v>
+        <v>260026000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №3/26</t>
+          <t>Оплата за сырье по дог. №178/26 от 24.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>26.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3654,23 +3649,23 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>18571000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>25637000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Xiva Logistik MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>234896196</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000371743824001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3680,14 +3675,14 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №199/26, QQS blan</t>
+          <t>Оплата за товар по счет-фактуре №3491 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3695,35 +3690,40 @@
           <t>177</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
-        <v>98100000</v>
-      </c>
-      <c r="D87" s="2" t="n"/>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n">
+        <v>35457000</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2207)</t>
+          <t>Qarshi Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>16307000204551232417</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2207 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по договору №134/26 от 27.08.2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,38 +3733,38 @@
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>8779000</v>
+        <v>171333000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Shartnoma №143/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №8866 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3774,38 +3774,38 @@
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>3546000</v>
+        <v>21323000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Nukus Mato XK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>267547195</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000704022068001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Shartnoma №4/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №8519 от 28.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3813,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>17562000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>28993000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №151/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №8933 от 31.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3856,38 +3856,38 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>3503000</v>
+        <v>19644000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4804 24.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №165/26 от 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3896,39 +3896,34 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>7527000</v>
+        <v>300000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>HISOB-KASSA XIZMATI UCHUN HAQ</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3936,40 +3931,40 @@
           <t>183</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>9738000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>42103000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №108/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №9049 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3977,40 +3972,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>43810000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>29627000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xiva Logistik MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>234896196</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000371743824001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №90/26</t>
+          <t>Shartnoma №109/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4020,38 +4015,38 @@
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>3408000</v>
+        <v>179110000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №492</t>
+          <t>Оплата по с/ф №2708 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4061,38 +4056,38 @@
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>302649000</v>
+        <v>20945000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7426</t>
+          <t>Оплата за товар по с/ф №2886 от 03.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4102,38 +4097,38 @@
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>7435000</v>
+        <v>14610000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Shartnoma №102/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по дог. №74/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4142,39 +4137,39 @@
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>2892000</v>
+        <v>5409000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bekobod Qurilish XK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>274288289</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000815144355001</t>
+          <t>20208000521839114001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №65/23</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4182,40 +4177,40 @@
           <t>189</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n"/>
-      <c r="D99" s="2" t="n">
-        <v>12093000</v>
-      </c>
+      <c r="C99" s="2" t="n">
+        <v>6257000</v>
+      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Mehnat Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>255105855</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000429346218001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1074 28.08.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №179/26</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4223,40 +4218,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n">
-        <v>5659000</v>
-      </c>
+      <c r="C100" s="2" t="n">
+        <v>11826000</v>
+      </c>
+      <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Samarqand Un Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>233823167</t>
+          <t>280179841</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000141435931001</t>
+          <t>20208000572420564001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7045 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по дог. №29/26</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4264,40 +4259,40 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>10087000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>13457000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Mehnat Agro Servis MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>255105855</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000429346218001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №92/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2956</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4305,40 +4300,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>7808000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>25414000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Oydin Plastik MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>289619633</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000174382470001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Shartnoma №131/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно с/ф №5171</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4346,40 +4341,35 @@
           <t>193</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>5001000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>60146000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>281194585</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SHARTNOMA №136/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №292</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4387,35 +4377,40 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>18937000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qarshi Tur Servis AJ</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Предоплата за товар по дог. №68/26 от 09.09.2026</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4424,39 +4419,39 @@
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>7889000</v>
+        <v>7478000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №1605</t>
+          <t>Оплата за транспортные услуги по дог. №231/26</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4464,40 +4459,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>12289000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>31236000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №253/26</t>
+          <t>Оплата за товар по с/ф №4951 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4505,40 +4500,40 @@
           <t>197</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>13666000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>13325000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6257</t>
+          <t>Оплата по счет-фактуре №7793 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4546,23 +4541,23 @@
           <t>198</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>34383000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>58239000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bog'ishamol Meva Eksport MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>256016118</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000519184114001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4572,14 +4567,14 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4391</t>
+          <t>Оплата по с/ф №2585 за поставленнй товар</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4587,23 +4582,23 @@
           <t>199</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>12560000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>57123000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4613,14 +4608,14 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №241/26</t>
+          <t>Оплата за продукцию по договору №144/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4628,23 +4623,23 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>21246000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>22097000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bog'ishamol Meva Eksport MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>256016118</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000519184114001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4654,14 +4649,14 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №105/26</t>
+          <t>Оплата за продукцию по дог. №7/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4670,39 +4665,39 @@
         </is>
       </c>
       <c r="C111" s="2" t="n">
-        <v>23268000</v>
+        <v>8202000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №282/26</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4710,40 +4705,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>18521000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>8202000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Shartnoma №105/26 bo'yicha oldindan to'lov</t>
+          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I AVGUST 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4752,39 +4747,39 @@
         </is>
       </c>
       <c r="C113" s="2" t="n">
-        <v>14156000</v>
+        <v>8787000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bog'ishamol Meva Eksport MChJ</t>
+          <t>Oydin Plastik MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>256016118</t>
+          <t>289619633</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000519184114001</t>
+          <t>20208000174382470001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №159/26</t>
+          <t>Оплата за сырье по договору №228/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4793,34 +4788,39 @@
         </is>
       </c>
       <c r="C114" s="2" t="n">
-        <v>60146000</v>
+        <v>4876000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Oqtosh Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>211426722</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000167815308001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Оплата за упаковочные материалы, с/ф №7826</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4828,40 +4828,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>103434000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>5757000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Guliston Trans Servis MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>224440088</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000363201573001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>SHARTNOMA №42/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товары согласно счет-фактуре №9404</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4869,23 +4869,23 @@
           <t>206</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n">
-        <v>47465000</v>
-      </c>
+      <c r="C116" s="2" t="n">
+        <v>8408000</v>
+      </c>
+      <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4895,14 +4895,14 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1369 07.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №132/26</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4912,38 +4912,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>44439000</v>
+        <v>114095000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6088</t>
+          <t>Оплата по счет-фактуре №3353 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>16.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4953,38 +4953,38 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>17912000</v>
+        <v>12457000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Saodat Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>314915911</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000334434907001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №19 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7818</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4992,23 +4992,23 @@
           <t>209</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>5409000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>66339000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ziyo Qurilish MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>266148204</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000217756169001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5018,14 +5018,14 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Предоплата за товар по договору №294/26 от 17.09.2026</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5034,22 +5034,22 @@
         </is>
       </c>
       <c r="C120" s="2" t="n">
-        <v>15384000</v>
+        <v>4949000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Nurafshon Dori-Darmon MChJ</t>
+          <t>Oydin Plastik MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>353894823</t>
+          <t>289619633</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000867104413001</t>
+          <t>20208000174382470001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5059,14 +5059,14 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №146/26, QQS bilan</t>
+          <t>Оплата за сырье по договору №103/26 от 17.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>17.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5075,22 +5075,22 @@
         </is>
       </c>
       <c r="C121" s="2" t="n">
-        <v>88481000</v>
+        <v>25594000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Oydin Plastik MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>289619633</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000174382470001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5100,14 +5100,14 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №156/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №4881</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5115,40 +5115,40 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>24069000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>6806000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Shahrisabz Avto Ehtiyot XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>306929805</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000432474335001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6320 09.09.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №126/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5156,40 +5156,40 @@
           <t>213</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>116635000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>74307000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Namangan Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>289482378</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000710441309001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №496 10.09.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №15/26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5198,39 +5198,39 @@
         </is>
       </c>
       <c r="C124" s="2" t="n">
-        <v>14355000</v>
+        <v>134937000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bog'ishamol Meva Eksport MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>256016118</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000519184114001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1519</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №108/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5239,39 +5239,34 @@
         </is>
       </c>
       <c r="C125" s="2" t="n">
-        <v>41319000</v>
+        <v>98100000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>231344019</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2207)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>16307000204551232417</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №246/26</t>
+          <t>Kredit shartnomasi L-2025-2207 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5279,40 +5274,40 @@
           <t>216</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>16874000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>7485000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>326149159</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000173344349001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Shartnoma №220/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №12/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5320,23 +5315,23 @@
           <t>217</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>43060000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>10132000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bog'ishamol Farm Savdo AJ</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>379269262</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000960347221001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5346,14 +5341,14 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>SHARTNOMA №20/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за транспортные услуги по договору №86/26</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>21.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5362,39 +5357,39 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>8202000</v>
+        <v>118031000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за товары согласно с/ф №8437</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5402,40 +5397,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>8202000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>15075000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6958</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5444,39 +5439,39 @@
         </is>
       </c>
       <c r="C130" s="2" t="n">
-        <v>227607000</v>
+        <v>8963000</v>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №94/26, QQS bilan</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5484,40 +5479,40 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>41651000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>13602000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Oydin Plastik MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>289619633</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000174382470001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5580 18.09.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №31/26 от 23.09.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5527,38 +5522,38 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>34400000</v>
+        <v>17955000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3319 18.09.2026, QQS BILAN</t>
+          <t>Оплата за продукцию по дог. №290/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5567,34 +5562,39 @@
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>98100000</v>
+        <v>5966000</v>
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2207)</t>
+          <t>Bahor Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>301611845</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>16307000204551232417</t>
+          <t>20208000918411424001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2207 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №261/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5604,38 +5604,38 @@
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>62545000</v>
+        <v>14341000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>233823167</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000141435931001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №22/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5644,39 +5644,39 @@
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>16298000</v>
+        <v>3380000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Angren Mato MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>244573432</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000147986957001</t>
+          <t>20208000802611443001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №234/26</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>28.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5685,39 +5685,39 @@
         </is>
       </c>
       <c r="C136" s="2" t="n">
-        <v>8976000</v>
+        <v>39467000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Предоплата за материалы по договору №259/26</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,40 +5725,40 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>25720000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>19313000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
+          <t>Qarshi Tur Servis AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>231344019</t>
+          <t>219458536</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000770640738001</t>
+          <t>20208000749293534001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №214/26</t>
+          <t>Оплата за продукцию по договору №21/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5766,40 +5766,35 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>22137000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>281194585</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7223</t>
+          <t>КОМИССИЯ ЗА ПЕРЕВОД</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>30.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5807,23 +5802,23 @@
           <t>229</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>25954000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>7997000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
+          <t>Qarshi Metall MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>281194585</t>
+          <t>392980554</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000647492935001</t>
+          <t>20208000247433591001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5833,397 +5828,33 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №288/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №212/26</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>25250000</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Shahrisabz Avto Ehtiyot XK</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>306929805</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>20208000432474335001</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №170/26, QQS 12%</t>
-        </is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="n">
+        <v>2057202000</v>
+      </c>
+      <c r="D140" s="4" t="n">
+        <v>2001902000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>16397000</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>281194585</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>20208000647492935001</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №246</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>3380000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>20208000815144355001</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>28.09.2026</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>12547000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Bog'ishamol Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>256016118</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>20208000519184114001</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №38/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>55539000</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Sarbon Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>326149159</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>20208000173344349001</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №215/26, QQS 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>29.09.2026</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>12600000</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Shahrisabz Avto Ehtiyot XK</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>306929805</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>20208000432474335001</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №4585 от 29.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>19134000</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Urganch Oziq-ovqat Savdo XK</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>281194585</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000647492935001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7688</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D147" s="2" t="n"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>30.09.2026</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>32167000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Bunyodkor Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>231344019</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>20208000770640738001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Xom ashyo uchun to'lov, shartn. №216/26, QQS bilan</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="n">
-        <v>2067265000</v>
-      </c>
-      <c r="D149" s="4" t="n">
-        <v>2011965000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C150" s="4" t="n">
+      <c r="C141" s="4" t="n">
         <v>299400000</v>
       </c>
-      <c r="D150" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
